--- a/employee_surveys/016_payroll_and_cryptocurrency_survey--employee_surveys.xlsx
+++ b/employee_surveys/016_payroll_and_cryptocurrency_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>preferred_currency</t>
+          <t>preferred_currency_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>preferred_currency</t>
+          <t>Preferred Currency 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>crypto_payment</t>
+          <t>crypto_payment_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>crypto_payment</t>
+          <t>Crypto Payment 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -894,7 +894,7 @@
   <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1446,7 +1446,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1480,7 +1480,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1497,7 +1497,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>preferred_currency_choices</t>
+          <t>preferred_currency_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1514,7 +1514,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>preferred_currency_choices</t>
+          <t>preferred_currency_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>preferred_currency_choices</t>
+          <t>preferred_currency_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1548,7 +1548,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>preferred_currency_choices</t>
+          <t>preferred_currency_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1565,7 +1565,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>preferred_currency_choices</t>
+          <t>preferred_currency_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1582,7 +1582,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>preferred_currency_choices</t>
+          <t>preferred_currency_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>preferred_currency_choices</t>
+          <t>preferred_currency_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>crypto_payment_choices</t>
+          <t>crypto_payment_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1633,7 +1633,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>crypto_payment_choices</t>
+          <t>crypto_payment_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
